--- a/originales/respuestas/2025/01. Calificadas/root/Instituto Distrital Para La Investigación Educativa Y El Desarrollo Pedagógico.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Instituto Distrital Para La Investigación Educativa Y El Desarrollo Pedagógico.xlsx
@@ -551,7 +551,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -593,6 +593,12 @@
       <u/>
       <sz val="10.0"/>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -676,7 +682,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -769,6 +775,9 @@
     </xf>
     <xf borderId="4" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8398,7 +8407,7 @@
       <c r="H10" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="31" t="s">
         <v>163</v>
       </c>
       <c r="J10" s="15"/>

--- a/originales/respuestas/2025/01. Calificadas/root/Instituto Distrital Para La Investigación Educativa Y El Desarrollo Pedagógico.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Instituto Distrital Para La Investigación Educativa Y El Desarrollo Pedagógico.xlsx
@@ -414,10 +414,10 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
-  </si>
-  <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 30.</t>
+  </si>
+  <si>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
@@ -762,7 +762,7 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -5624,7 +5624,7 @@
       <c r="C19" s="11">
         <v>18.0</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="12" t="s">
         <v>125</v>
       </c>
       <c r="E19" s="10"/>
